--- a/excel/items.xlsx
+++ b/excel/items.xlsx
@@ -6055,7 +6055,7 @@
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G122" s="7"/>
       <c r="H122" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="G135" s="7"/>
       <c r="H135" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="G138" s="7"/>
       <c r="H138" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="G139" s="7"/>
       <c r="H139" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="G140" s="7"/>
       <c r="H140" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="G141" s="7"/>
       <c r="H141" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G142" s="7"/>
       <c r="H142" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="G143" s="7"/>
       <c r="H143" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="G144" s="7"/>
       <c r="H144" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="G146" s="7"/>
       <c r="H146" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G147" s="7"/>
       <c r="H147" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="G148" s="7"/>
       <c r="H148" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G149" s="7"/>
       <c r="H149" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G150" s="7"/>
       <c r="H150" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="G151" s="7"/>
       <c r="H151" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="G152" s="7"/>
       <c r="H152" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -7200,14 +7200,14 @@
         <v>3</v>
       </c>
       <c r="E153" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F153" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G153" s="7"/>
       <c r="H153" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -7224,14 +7224,14 @@
         <v>3</v>
       </c>
       <c r="E154" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F154" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G154" s="7"/>
       <c r="H154" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -7248,14 +7248,14 @@
         <v>3</v>
       </c>
       <c r="E155" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F155" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G155" s="7"/>
       <c r="H155" s="7">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -7272,14 +7272,14 @@
         <v>3</v>
       </c>
       <c r="E156" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F156" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G156" s="7"/>
       <c r="H156" s="7">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -7296,14 +7296,14 @@
         <v>3</v>
       </c>
       <c r="E157" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F157" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G157" s="7"/>
       <c r="H157" s="7">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G158" s="9"/>
       <c r="H158" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="G159" s="9"/>
       <c r="H159" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="G160" s="9"/>
       <c r="H160" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G161" s="9"/>
       <c r="H161" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="G162" s="9"/>
       <c r="H162" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="G163" s="9"/>
       <c r="H163" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="G164" s="9"/>
       <c r="H164" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="G165" s="9"/>
       <c r="H165" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="G166" s="9"/>
       <c r="H166" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="G167" s="9"/>
       <c r="H167" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="G168" s="9"/>
       <c r="H168" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G169" s="9"/>
       <c r="H169" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="G170" s="9"/>
       <c r="H170" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="G171" s="9"/>
       <c r="H171" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="G172" s="9"/>
       <c r="H172" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="G173" s="9"/>
       <c r="H173" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="G174" s="9"/>
       <c r="H174" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="G175" s="9"/>
       <c r="H175" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="G176" s="9"/>
       <c r="H176" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="G177" s="9"/>
       <c r="H177" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G178" s="9"/>
       <c r="H178" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="G179" s="9"/>
       <c r="H179" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G180" s="9"/>
       <c r="H180" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="G181" s="9"/>
       <c r="H181" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="G182" s="9"/>
       <c r="H182" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="G183" s="9"/>
       <c r="H183" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G184" s="9"/>
       <c r="H184" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="G185" s="9"/>
       <c r="H185" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="G186" s="9"/>
       <c r="H186" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="G187" s="9"/>
       <c r="H187" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G188" s="9"/>
       <c r="H188" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G189" s="9"/>
       <c r="H189" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="G190" s="9"/>
       <c r="H190" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="G191" s="9"/>
       <c r="H191" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="G192" s="9"/>
       <c r="H192" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="G193" s="9"/>
       <c r="H193" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="G194" s="9"/>
       <c r="H194" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="G195" s="9"/>
       <c r="H195" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G196" s="9"/>
       <c r="H196" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="G197" s="9"/>
       <c r="H197" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="G198" s="9"/>
       <c r="H198" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G199" s="9"/>
       <c r="H199" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="G200" s="9"/>
       <c r="H200" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="G201" s="9"/>
       <c r="H201" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="G202" s="9"/>
       <c r="H202" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="G203" s="9"/>
       <c r="H203" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="G204" s="9"/>
       <c r="H204" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="G205" s="9"/>
       <c r="H205" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="G206" s="9"/>
       <c r="H206" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G207" s="9"/>
       <c r="H207" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="G208" s="9"/>
       <c r="H208" s="9">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="G209" s="9"/>
       <c r="H209" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="G210" s="9"/>
       <c r="H210" s="9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="G251" s="11"/>
       <c r="H251" s="11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="G257" s="11"/>
       <c r="H257" s="11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="G261" s="11"/>
       <c r="H261" s="11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="G267" s="11"/>
       <c r="H267" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="G268" s="11"/>
       <c r="H268" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="G269" s="11"/>
       <c r="H269" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G270" s="5"/>
       <c r="H270" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="G271" s="5"/>
       <c r="H271" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="G272" s="5"/>
       <c r="H272" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="G273" s="5"/>
       <c r="H273" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G274" s="5"/>
       <c r="H274" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G275" s="5"/>
       <c r="H275" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="G276" s="5"/>
       <c r="H276" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="G277" s="5"/>
       <c r="H277" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="G278" s="5"/>
       <c r="H278" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="G279" s="5"/>
       <c r="H279" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="G280" s="5"/>
       <c r="H280" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="G281" s="5"/>
       <c r="H281" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="G282" s="5"/>
       <c r="H282" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G283" s="5"/>
       <c r="H283" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="G284" s="5"/>
       <c r="H284" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="G287" s="5"/>
       <c r="H287" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="G288" s="5"/>
       <c r="H288" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G289" s="5"/>
       <c r="H289" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="G290" s="5"/>
       <c r="H290" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="G291" s="5"/>
       <c r="H291" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="G292" s="5"/>
       <c r="H292" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="G293" s="5"/>
       <c r="H293" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G294" s="5"/>
       <c r="H294" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="G295" s="5"/>
       <c r="H295" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="G296" s="5"/>
       <c r="H296" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="G297" s="5"/>
       <c r="H297" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="G298" s="5"/>
       <c r="H298" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="G299" s="5"/>
       <c r="H299" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G300" s="5"/>
       <c r="H300" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="G301" s="5"/>
       <c r="H301" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="G302" s="5"/>
       <c r="H302" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="G303" s="5"/>
       <c r="H303" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="G304" s="5"/>
       <c r="H304" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G305" s="5"/>
       <c r="H305" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="G307" s="5"/>
       <c r="H307" s="5">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="G308" s="5"/>
       <c r="H308" s="5">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="G309" s="5"/>
       <c r="H309" s="5">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G310" s="5"/>
       <c r="H310" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="G311" s="5"/>
       <c r="H311" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="G312" s="5"/>
       <c r="H312" s="5">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G313" s="5"/>
       <c r="H313" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="G314" s="5"/>
       <c r="H314" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="G315" s="5"/>
       <c r="H315" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="G316" s="5"/>
       <c r="H316" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="G317" s="5"/>
       <c r="H317" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="G318" s="5"/>
       <c r="H318" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="G319" s="5"/>
       <c r="H319" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="G320" s="5"/>
       <c r="H320" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="G322" s="5"/>
       <c r="H322" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="G323" s="5"/>
       <c r="H323" s="5">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="G324" s="5"/>
       <c r="H324" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="G325" s="5"/>
       <c r="H325" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="G326" s="5"/>
       <c r="H326" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="G327" s="5"/>
       <c r="H327" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -12606,7 +12606,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H2 A3:D3 F3:H3 A4 D4 F4 A5:A22" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:A22 F4 D4 F3:H3 A3:D3 A1:H2" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
